--- a/financeiro/2026-07/vendas.xlsx
+++ b/financeiro/2026-07/vendas.xlsx
@@ -464,10 +464,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>6480</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="4">
